--- a/Results/Two_Datasets_Assessment/Cancer/Processed_Data/privacy_scores.xlsx
+++ b/Results/Two_Datasets_Assessment/Cancer/Processed_Data/privacy_scores.xlsx
@@ -475,13 +475,13 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5363147907251201</v>
+        <v>0.6670557325674165</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4520312730149757</v>
+        <v>0.3020752481436006</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -499,13 +499,13 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3123008246014149</v>
+        <v>0.2013340430684206</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3977363801222663</v>
+        <v>0.2911875017735279</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -523,13 +523,13 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3801171918778428</v>
+        <v>0.1717370163302168</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3416095923426357</v>
+        <v>0.2943798743041575</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -547,13 +547,13 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7458789484729241</v>
+        <v>0.7279601106252133</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4306859916848103</v>
+        <v>0.3868807022146142</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -571,13 +571,13 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6147824256659962</v>
+        <v>0.8121587739421542</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3948195200317383</v>
+        <v>0.344598893877038</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -595,13 +595,13 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4877173849809624</v>
+        <v>0.5817496483258702</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4592444829575035</v>
+        <v>0.3266270920749452</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -619,13 +619,13 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4597927818721145</v>
+        <v>0.7201306164880913</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4618239786791074</v>
+        <v>0.3716551046688774</v>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -643,13 +643,13 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5695028378343651</v>
+        <v>0.7262959665789475</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4284281443663037</v>
+        <v>0.3734551008039336</v>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
